--- a/Open Gym Schedules (Print).xlsx
+++ b/Open Gym Schedules (Print).xlsx
@@ -13,16 +13,18 @@
     <sheet name="4 team - Short" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="5 team - Long" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="5 team - Short" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="6 team" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="6 team - waves" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="6 team - by section" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'2 team'!$A$1:$D$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'3 team'!$A$1:$D$29</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'4 team - Long'!$A$1:$D$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'4 team - Short'!$A$1:$D$20</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'5 team - Long'!$A$1:$D$38</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'5 team - Short'!$A$1:$D$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'6 team'!$A$1:$D$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'2 team'!$A$1:$E$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'3 team'!$A$1:$E$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'4 team - Long'!$A$1:$E$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'4 team - Short'!$A$1:$E$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'5 team - Long'!$A$1:$E$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'5 team - Short'!$A$1:$E$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'6 team - waves'!$A$1:$F$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'6 team - by section'!$A$1:$E$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,13 +86,47 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00AAAAAA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -110,27 +146,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -498,13 +540,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,172 +556,205 @@
           <t>Section 1</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Rd 1</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Rd 2</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n"/>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Rd 3</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Rd 4</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Rd 5</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Rd 6</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Rd 7</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Rd 8</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -686,172 +762,205 @@
           <t>Section 2</t>
         </is>
       </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Rd 9</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n"/>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Rd 10</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Rd 11</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Rd 12</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n"/>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Rd 13</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Rd 14</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n"/>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Rd 15</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Rd 16</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n"/>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -859,172 +968,205 @@
           <t>Section 3</t>
         </is>
       </c>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="3" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Rd 1</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n"/>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Rd 2</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n"/>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Rd 3</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n"/>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Rd 4</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n"/>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Rd 5</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n"/>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Rd 6</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n"/>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Rd 7</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n"/>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Rd 8</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n"/>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1032,179 +1174,212 @@
           <t>Section 4</t>
         </is>
       </c>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="3" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Rd 9</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n"/>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Rd 10</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n"/>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Rd 11</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n"/>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Rd 12</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n"/>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Rd 13</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n"/>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Rd 14</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n"/>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Rd 15</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n"/>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Rd 16</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n"/>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1217,13 +1392,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1232,244 +1408,289 @@
           <t>Section 1</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Rd 1</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Rd 2</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n"/>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Rd 3</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Rd 4</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Rd 5</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Rd 6</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Rd 7</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Rd 8</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n"/>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Rd 9</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n"/>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Rd 10</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Rd 11</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Rd 12</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1477,249 +1698,294 @@
           <t>Section 2</t>
         </is>
       </c>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Rd 13</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Rd 14</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n"/>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Rd 15</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Rd 16</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n"/>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Rd 17</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n"/>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Rd 18</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Rd 19</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n"/>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Rd 20</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n"/>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Rd 21</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Rd 22</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n"/>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Rd 23</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n"/>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>Rd 24</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n"/>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1732,13 +1998,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1747,172 +2014,205 @@
           <t>Section 1</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Rd 1</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Rd 2</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n"/>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Rd 3</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Rd 4</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Rd 5</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Rd 6</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Rd 7</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Rd 8</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n"/>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1920,172 +2220,205 @@
           <t>Section 2</t>
         </is>
       </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Rd 1</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n"/>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Rd 2</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Rd 3</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Rd 4</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n"/>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Rd 5</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Rd 6</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n"/>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Rd 7</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Rd 8</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n"/>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -2093,178 +2426,211 @@
           <t>Section 3</t>
         </is>
       </c>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="3" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Rd 1</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n"/>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Rd 2</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n"/>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Rd 3</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n"/>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Rd 4</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n"/>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Rd 5</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n"/>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Rd 6</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n"/>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Rd 7</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n"/>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Rd 8</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n"/>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2277,13 +2643,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2292,100 +2659,121 @@
           <t>Section 1</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Rd 1</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Rd 2</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n"/>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Rd 3</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Rd 4</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2393,100 +2781,121 @@
           <t>Section 2</t>
         </is>
       </c>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Rd 1</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n"/>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Rd 2</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n"/>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Rd 3</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Rd 4</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -2494,106 +2903,127 @@
           <t>Section 3</t>
         </is>
       </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Rd 1</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Rd 2</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n"/>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Rd 3</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n"/>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Rd 4</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2606,13 +3036,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2621,208 +3052,247 @@
           <t>Section 1</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Rd 1</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Rd 2</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n"/>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Rd 3</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Rd 4</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Rd 5</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Rd 6</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Rd 7</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Rd 8</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n"/>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Rd 9</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n"/>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Rd 10</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -2830,208 +3300,247 @@
           <t>Section 2</t>
         </is>
       </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Rd 1</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="7" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Rd 2</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n"/>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Rd 3</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Rd 4</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n"/>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Rd 5</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Rd 6</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="7" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Rd 7</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n"/>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Rd 8</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Rd 9</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n"/>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Rd 10</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n"/>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -3039,214 +3548,253 @@
           <t>Section 3</t>
         </is>
       </c>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="3" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Rd 1</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n"/>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Rd 2</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Rd 3</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n"/>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Rd 4</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n"/>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Rd 5</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n"/>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Rd 6</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n"/>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Rd 7</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="7" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Rd 8</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n"/>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Rd 9</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n"/>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Rd 10</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n"/>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3259,13 +3807,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3274,118 +3823,142 @@
           <t>Section 1</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Rd 1</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Rd 2</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n"/>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Rd 3</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Rd 4</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Rd 5</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -3393,118 +3966,142 @@
           <t>Section 2</t>
         </is>
       </c>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Rd 1</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Rd 2</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Rd 3</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Rd 4</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n"/>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Rd 5</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -3512,124 +4109,148 @@
           <t>Section 3</t>
         </is>
       </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Rd 1</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n"/>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Rd 2</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="7" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Rd 3</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n"/>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Rd 4</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n"/>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Rd 5</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n"/>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A17:E17"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3642,151 +4263,1194 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Winner</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Rd 1</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Rd 1</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Rd 1</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Team 6</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Rd 1</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Team 5</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Rd 1</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Team 6</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Wave 2</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Winner</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Rd 2</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Rd 2</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Team 5</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Rd 2</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Rd 2</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Rd 2</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Team 5</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Wave 3</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Winner</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Rd 3</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Team 5</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Team 6</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Rd 3</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Team 6</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Rd 3</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Team 5</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Rd 3</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Team 6</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Rd 3</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Wave 4</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Winner</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Rd 4</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Rd 4</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Rd 4</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Team 6</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Rd 4</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Team 5</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Rd 4</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Team 6</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Wave 5</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Winner</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Rd 5</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B36" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Rd 5</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>Team 5</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Rd 5</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B38" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Rd 5</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Rd 5</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Team 5</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Wave 6</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Winner</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Rd 6</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Team 6</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Team 5</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B44" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Rd 6</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>Team 6</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Rd 6</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Team 5</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B46" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Rd 6</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>Team 6</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Rd 6</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A25:F25"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
           <t>Section 1</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Rd 1</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Rd 2</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n"/>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Rd 3</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Team 6</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Rd 4</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Rd 5</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Rd 6</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Team 6</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -3794,136 +5458,163 @@
           <t>Section 2</t>
         </is>
       </c>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Rd 1</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Rd 2</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Rd 3</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Team 6</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Rd 4</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Rd 5</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n"/>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Rd 6</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Team 6</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n"/>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -3931,136 +5622,163 @@
           <t>Section 3</t>
         </is>
       </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Rd 1</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Team 6</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="7" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Rd 2</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n"/>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Rd 3</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="7" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Rd 4</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Team 6</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n"/>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Rd 5</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n"/>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Rd 6</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n"/>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -4068,136 +5786,163 @@
           <t>Section 4</t>
         </is>
       </c>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Rd 1</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Rd 2</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n"/>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Rd 3</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>Team 6</t>
         </is>
       </c>
-      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="7" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Rd 4</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n"/>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Rd 5</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n"/>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="A35" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Rd 6</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>Team 6</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n"/>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -4205,144 +5950,171 @@
           <t>Section 5</t>
         </is>
       </c>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="3" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Rd 1</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>Team 6</t>
         </is>
       </c>
-      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="7" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Rd 2</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="7" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Rd 3</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n"/>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Rd 4</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>Team 6</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>Team 4</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n"/>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>Team 4</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Rd 5</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>Team 5</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Team 1</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n"/>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Team 1</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="A44" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>Rd 6</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Team 3</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Team 2</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n"/>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Team 3</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>Team 2</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A37:E37"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
